--- a/public/downloads/ComerGeneralized2024.xlsx
+++ b/public/downloads/ComerGeneralized2024.xlsx
@@ -8,37 +8,39 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="6" r:id="rId6"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="7" r:id="rId7"/>
-    <sheet name="eSEN-30M-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="GRACE-2L-OAM" sheetId="9" r:id="rId9"/>
-    <sheet name="MACE-MH-1-OC20" sheetId="10" r:id="rId10"/>
-    <sheet name="MACE-MH-1-OMAT" sheetId="11" r:id="rId11"/>
-    <sheet name="MACE-MPA-0" sheetId="12" r:id="rId12"/>
-    <sheet name="MATLANTISv8" sheetId="13" r:id="rId13"/>
-    <sheet name="MatterSim_v1_5M" sheetId="14" r:id="rId14"/>
-    <sheet name="NequIP-OAM-L" sheetId="15" r:id="rId15"/>
-    <sheet name="NequIP-OAM-XL" sheetId="16" r:id="rId16"/>
-    <sheet name="Nequix-MP-1" sheetId="17" r:id="rId17"/>
-    <sheet name="ORB-v3" sheetId="18" r:id="rId18"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="19" r:id="rId19"/>
-    <sheet name="SevenNet-Omni" sheetId="20" r:id="rId20"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="21" r:id="rId21"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="22" r:id="rId22"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="23" r:id="rId23"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="24" r:id="rId24"/>
-    <sheet name="UMA-s-1p2_oc22" sheetId="25" r:id="rId25"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="8" r:id="rId8"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="9" r:id="rId9"/>
+    <sheet name="eSEN-30M-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="GRACE-2L-OAM" sheetId="11" r:id="rId11"/>
+    <sheet name="MACE-MH-1-OC20" sheetId="12" r:id="rId12"/>
+    <sheet name="MACE-MH-1-OMAT" sheetId="13" r:id="rId13"/>
+    <sheet name="MACE-MPA-0" sheetId="14" r:id="rId14"/>
+    <sheet name="MATLANTISv8" sheetId="15" r:id="rId15"/>
+    <sheet name="MatterSim_v1_5M" sheetId="16" r:id="rId16"/>
+    <sheet name="NequIP-OAM-L" sheetId="17" r:id="rId17"/>
+    <sheet name="NequIP-OAM-XL" sheetId="18" r:id="rId18"/>
+    <sheet name="Nequix-MP-1" sheetId="19" r:id="rId19"/>
+    <sheet name="ORB-v3" sheetId="20" r:id="rId20"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="21" r:id="rId21"/>
+    <sheet name="SevenNet-Omni" sheetId="22" r:id="rId22"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="23" r:id="rId23"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="24" r:id="rId24"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="25" r:id="rId25"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="26" r:id="rId26"/>
+    <sheet name="UMA-s-1p2_oc22" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="62">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -70,10 +72,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -197,6 +199,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>OH</t>
@@ -688,10 +711,10 @@
         <v>325</v>
       </c>
       <c r="N3" s="5">
-        <v>855.6279256343842</v>
+        <v>855627.9256343842</v>
       </c>
       <c r="O3" s="4">
-        <v>0.01815232360901188</v>
+        <v>18.15232360901188</v>
       </c>
       <c r="P3" s="5">
         <v>47136</v>
@@ -738,10 +761,10 @@
         <v>325</v>
       </c>
       <c r="N4" s="5">
-        <v>4192.900455713272</v>
+        <v>4192900.455713272</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03391930085357057</v>
+        <v>33.91930085357057</v>
       </c>
       <c r="P4" s="5">
         <v>123614</v>
@@ -788,10 +811,10 @@
         <v>325</v>
       </c>
       <c r="N5" s="5">
-        <v>2629.788564443588</v>
+        <v>2629788.564443588</v>
       </c>
       <c r="O5" s="4">
-        <v>0.04531774193423382</v>
+        <v>45.31774193423382</v>
       </c>
       <c r="P5" s="5">
         <v>58030</v>
@@ -838,10 +861,10 @@
         <v>325</v>
       </c>
       <c r="N6" s="5">
-        <v>8470.603838443756</v>
+        <v>8470603.838443756</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1351102791087465</v>
+        <v>135.1102791087465</v>
       </c>
       <c r="P6" s="5">
         <v>62694</v>
@@ -888,10 +911,10 @@
         <v>325</v>
       </c>
       <c r="N7" s="5">
-        <v>6892.472770452499</v>
+        <v>6892472.770452499</v>
       </c>
       <c r="O7" s="4">
-        <v>0.08753457925390525</v>
+        <v>87.53457925390525</v>
       </c>
       <c r="P7" s="5">
         <v>78740</v>
@@ -938,10 +961,10 @@
         <v>325</v>
       </c>
       <c r="N8" s="5">
-        <v>8520.227988004684</v>
+        <v>8520227.988004684</v>
       </c>
       <c r="O8" s="4">
-        <v>0.160232970775279</v>
+        <v>160.232970775279</v>
       </c>
       <c r="P8" s="5">
         <v>53174</v>
@@ -988,10 +1011,10 @@
         <v>325</v>
       </c>
       <c r="N9" s="5">
-        <v>1465.264305591583</v>
+        <v>1465264.305591583</v>
       </c>
       <c r="O9" s="4">
-        <v>0.01283630578704847</v>
+        <v>12.83630578704847</v>
       </c>
       <c r="P9" s="5">
         <v>114150</v>
@@ -1038,10 +1061,10 @@
         <v>325</v>
       </c>
       <c r="N10" s="5">
-        <v>7614.875867128372</v>
+        <v>7614875.867128372</v>
       </c>
       <c r="O10" s="4">
-        <v>0.06086495885356501</v>
+        <v>60.86495885356501</v>
       </c>
       <c r="P10" s="5">
         <v>125111</v>
@@ -1088,10 +1111,10 @@
         <v>325</v>
       </c>
       <c r="N11" s="5">
-        <v>3456.411633014679</v>
+        <v>3456411.633014679</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05901334527940377</v>
+        <v>59.01334527940377</v>
       </c>
       <c r="P11" s="5">
         <v>58570</v>
@@ -1138,10 +1161,10 @@
         <v>325</v>
       </c>
       <c r="N12" s="5">
-        <v>6240.330505371094</v>
+        <v>6240330.505371094</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0606634765463613</v>
+        <v>60.6634765463613</v>
       </c>
       <c r="P12" s="5">
         <v>102868</v>
@@ -1188,10 +1211,10 @@
         <v>325</v>
       </c>
       <c r="N13" s="5">
-        <v>9603.457632780075</v>
+        <v>9603457.632780075</v>
       </c>
       <c r="O13" s="4">
-        <v>0.09285521380704745</v>
+        <v>92.85521380704745</v>
       </c>
       <c r="P13" s="5">
         <v>103424</v>
@@ -1238,10 +1261,10 @@
         <v>325</v>
       </c>
       <c r="N14" s="5">
-        <v>3539.883114099503</v>
+        <v>3539883.114099503</v>
       </c>
       <c r="O14" s="4">
-        <v>0.04137214083471053</v>
+        <v>41.37214083471053</v>
       </c>
       <c r="P14" s="5">
         <v>85562</v>
@@ -1288,10 +1311,10 @@
         <v>325</v>
       </c>
       <c r="N15" s="5">
-        <v>386.7497234344482</v>
+        <v>386749.7234344482</v>
       </c>
       <c r="O15" s="4">
-        <v>0.006827244093956507</v>
+        <v>6.827244093956507</v>
       </c>
       <c r="P15" s="5">
         <v>56648</v>
@@ -1338,10 +1361,10 @@
         <v>325</v>
       </c>
       <c r="N16" s="5">
-        <v>650.0870826244354</v>
+        <v>650087.0826244354</v>
       </c>
       <c r="O16" s="4">
-        <v>0.0112686268438973</v>
+        <v>11.2686268438973</v>
       </c>
       <c r="P16" s="5">
         <v>57690</v>
@@ -1388,10 +1411,10 @@
         <v>325</v>
       </c>
       <c r="N17" s="5">
-        <v>1288.668076515198</v>
+        <v>1288668.076515198</v>
       </c>
       <c r="O17" s="4">
-        <v>0.01698498868494152</v>
+        <v>16.98498868494152</v>
       </c>
       <c r="P17" s="5">
         <v>75871</v>
@@ -1438,10 +1461,10 @@
         <v>325</v>
       </c>
       <c r="N18" s="5">
-        <v>701.1735091209412</v>
+        <v>701173.5091209412</v>
       </c>
       <c r="O18" s="4">
-        <v>0.01835917231674019</v>
+        <v>18.35917231674019</v>
       </c>
       <c r="P18" s="5">
         <v>38192</v>
@@ -1488,10 +1511,10 @@
         <v>325</v>
       </c>
       <c r="N19" s="5">
-        <v>9100.794110298157</v>
+        <v>9100794.110298157</v>
       </c>
       <c r="O19" s="4">
-        <v>0.07583615911119575</v>
+        <v>75.83615911119574</v>
       </c>
       <c r="P19" s="5">
         <v>120006</v>
@@ -1538,10 +1561,10 @@
         <v>325</v>
       </c>
       <c r="N20" s="5">
-        <v>5874.303419113159</v>
+        <v>5874303.419113159</v>
       </c>
       <c r="O20" s="4">
-        <v>0.08626629589710198</v>
+        <v>86.26629589710198</v>
       </c>
       <c r="P20" s="5">
         <v>68095</v>
@@ -1588,10 +1611,10 @@
         <v>325</v>
       </c>
       <c r="N21" s="5">
-        <v>20284.77910375595</v>
+        <v>20284779.10375595</v>
       </c>
       <c r="O21" s="4">
-        <v>0.1601982191525706</v>
+        <v>160.1982191525706</v>
       </c>
       <c r="P21" s="5">
         <v>126623</v>
@@ -1638,10 +1661,10 @@
         <v>325</v>
       </c>
       <c r="N22" s="5">
-        <v>9425.951847314835</v>
+        <v>9425951.847314835</v>
       </c>
       <c r="O22" s="4">
-        <v>0.2264873815972616</v>
+        <v>226.4873815972616</v>
       </c>
       <c r="P22" s="5">
         <v>41618</v>
@@ -1688,10 +1711,10 @@
         <v>325</v>
       </c>
       <c r="N23" s="5">
-        <v>16253.58920526505</v>
+        <v>16253589.20526505</v>
       </c>
       <c r="O23" s="4">
-        <v>0.09143558283789967</v>
+        <v>91.43558283789967</v>
       </c>
       <c r="P23" s="5">
         <v>177760</v>
@@ -1738,10 +1761,10 @@
         <v>325</v>
       </c>
       <c r="N24" s="5">
-        <v>4957.560059309006</v>
+        <v>4957560.059309006</v>
       </c>
       <c r="O24" s="4">
-        <v>0.100136544786883</v>
+        <v>100.136544786883</v>
       </c>
       <c r="P24" s="5">
         <v>49508</v>
@@ -1788,10 +1811,10 @@
         <v>325</v>
       </c>
       <c r="N25" s="5">
-        <v>4600.856693506241</v>
+        <v>4600856.693506241</v>
       </c>
       <c r="O25" s="4">
-        <v>0.08836246242425752</v>
+        <v>88.36246242425752</v>
       </c>
       <c r="P25" s="5">
         <v>52068</v>
@@ -1819,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1830,9 +1853,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -1866,8 +1895,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1889,91 +1926,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4991899103413574</v>
+        <v>0.1334796414541707</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2459376011585812</v>
+        <v>0.1113602338075775</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2351880896579875</v>
+        <v>0.1124726852400128</v>
       </c>
       <c r="E3" s="4">
-        <v>75.46721756187137</v>
+        <v>85.52522849630607</v>
       </c>
       <c r="F3" s="4">
-        <v>80.54590247182871</v>
+        <v>88.62464144055073</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K3" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.03692850509497017</v>
+      </c>
+      <c r="O3" s="5">
+        <v>142</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.130511472655447</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1081994266352257</v>
+      </c>
+      <c r="R3" s="5">
+        <v>142</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7629752504992121</v>
+        <v>0.2914227144717063</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2498319753781632</v>
+        <v>0.1557206276096344</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2971911810342044</v>
+        <v>0.1635042643834083</v>
       </c>
       <c r="E4" s="4">
-        <v>75.49088771310952</v>
+        <v>85.50642479213948</v>
       </c>
       <c r="F4" s="4">
-        <v>79.5709393211276</v>
+        <v>88.25869307039834</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.03136983913752948</v>
+      </c>
+      <c r="O4" s="5">
+        <v>139</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2872939672800265</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1523519600511608</v>
+      </c>
+      <c r="R4" s="5">
+        <v>139</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1984,6 +2075,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1991,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2002,9 +2094,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2038,8 +2136,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2061,91 +2167,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2706353306465974</v>
+        <v>0.3375487983527011</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1768805290272119</v>
+        <v>0.2069333034833312</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1613305119905767</v>
+        <v>0.2004904754396683</v>
       </c>
       <c r="E3" s="4">
-        <v>80.72701473227326</v>
+        <v>76.4625850340138</v>
       </c>
       <c r="F3" s="4">
-        <v>84.60122699386571</v>
+        <v>80.09374013532516</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="I3" s="5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J3" s="5">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03638818208920176</v>
+      </c>
+      <c r="O3" s="5">
+        <v>117</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.335778405165628</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.206954939100602</v>
+      </c>
+      <c r="R3" s="5">
+        <v>117</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4292398074750226</v>
+        <v>0.382396778675601</v>
       </c>
       <c r="C4" s="4">
-        <v>0.220577104866723</v>
+        <v>0.2451190038609061</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2208497418282105</v>
+        <v>0.2364093265442755</v>
       </c>
       <c r="E4" s="4">
-        <v>81.95998152347404</v>
+        <v>79.71928277483855</v>
       </c>
       <c r="F4" s="4">
-        <v>85.97826387162469</v>
+        <v>83.70874416549094</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.044521040269076</v>
+      </c>
+      <c r="O4" s="5">
+        <v>127</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3765470941426483</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2389131796896986</v>
+      </c>
+      <c r="R4" s="5">
+        <v>127</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2156,6 +2316,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2163,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2174,9 +2335,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2210,8 +2377,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2233,91 +2408,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6336285084559274</v>
+        <v>0.4991899103413574</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4255610503051269</v>
+        <v>0.2459376011585812</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4166377888180631</v>
+        <v>0.2351880896579875</v>
       </c>
       <c r="E3" s="4">
-        <v>70.36162931430238</v>
+        <v>75.46721756187137</v>
       </c>
       <c r="F3" s="4">
-        <v>75.93870520580127</v>
+        <v>80.54590247182871</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I3" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L3" s="5">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.04679944285546225</v>
+      </c>
+      <c r="O3" s="5">
+        <v>134</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4919916928218739</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2324167314832145</v>
+      </c>
+      <c r="R3" s="5">
+        <v>133</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6108346361554351</v>
+        <v>0.7629752504992121</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3766849358692391</v>
+        <v>0.2498319753781632</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3585851377782064</v>
+        <v>0.2971911810342044</v>
       </c>
       <c r="E4" s="4">
-        <v>72.67888636936237</v>
+        <v>75.49088771310952</v>
       </c>
       <c r="F4" s="4">
-        <v>78.56547076532357</v>
+        <v>79.5709393211276</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L4" s="5">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.09982157691023757</v>
+      </c>
+      <c r="O4" s="5">
+        <v>124</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7456533763439384</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.256706269895459</v>
+      </c>
+      <c r="R4" s="5">
+        <v>123</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2328,6 +2557,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2335,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2346,9 +2576,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2382,8 +2618,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2405,91 +2649,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3993395345150279</v>
+        <v>0.2706353306465974</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1700016509153101</v>
+        <v>0.1768805290272119</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1564113769391631</v>
+        <v>0.1613305119905767</v>
       </c>
       <c r="E3" s="4">
-        <v>78.5463878803054</v>
+        <v>80.72701473227326</v>
       </c>
       <c r="F3" s="4">
-        <v>82.58032417891555</v>
+        <v>84.60122699386571</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="I3" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K3" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.06043501542106314</v>
+      </c>
+      <c r="O3" s="5">
+        <v>136</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2660889121994475</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1759215006019529</v>
+      </c>
+      <c r="R3" s="5">
+        <v>136</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4545102636349851</v>
+        <v>0.4292398074750226</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2155336650992488</v>
+        <v>0.220577104866723</v>
       </c>
       <c r="D4" s="4">
-        <v>0.217164744968518</v>
+        <v>0.2208497418282105</v>
       </c>
       <c r="E4" s="4">
-        <v>80.75480809607805</v>
+        <v>81.95998152347404</v>
       </c>
       <c r="F4" s="4">
-        <v>84.33845665202608</v>
+        <v>85.97826387162469</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K4" s="5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.09154147178202492</v>
+      </c>
+      <c r="O4" s="5">
+        <v>143</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4213213564777702</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2145823701025778</v>
+      </c>
+      <c r="R4" s="5">
+        <v>143</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2500,6 +2798,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2507,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2518,9 +2817,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2554,8 +2859,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2577,91 +2890,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.373279281509418</v>
+        <v>0.6336285084559274</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1944698319512345</v>
+        <v>0.4255610503051269</v>
       </c>
       <c r="D3" s="4">
-        <v>0.194933532753765</v>
+        <v>0.4166377888180631</v>
       </c>
       <c r="E3" s="4">
-        <v>77.11468636534357</v>
+        <v>70.36162931430238</v>
       </c>
       <c r="F3" s="4">
-        <v>79.60081525095676</v>
+        <v>75.93870520580127</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I3" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3953948319280088</v>
+      </c>
+      <c r="O3" s="5">
+        <v>115</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4635009279515714</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.261100097042874</v>
+      </c>
+      <c r="R3" s="5">
+        <v>115</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.491991344489324</v>
+        <v>0.6108346361554351</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2176778804907421</v>
+        <v>0.3766849358692391</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2225699824050865</v>
+        <v>0.3585851377782064</v>
       </c>
       <c r="E4" s="4">
-        <v>78.69383555891503</v>
+        <v>72.67888636936237</v>
       </c>
       <c r="F4" s="4">
-        <v>81.98739194078576</v>
+        <v>78.56547076532357</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K4" s="5">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2764046367147363</v>
+      </c>
+      <c r="O4" s="5">
+        <v>116</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4938189534859734</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2664669001928559</v>
+      </c>
+      <c r="R4" s="5">
+        <v>116</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2672,6 +3039,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2679,7 +3047,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2690,9 +3058,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2726,8 +3100,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2749,91 +3131,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>1.378798811061967</v>
+        <v>0.3993395345150279</v>
       </c>
       <c r="C3" s="4">
-        <v>1.090417123643917</v>
+        <v>0.1700016509153101</v>
       </c>
       <c r="D3" s="4">
-        <v>1.459599411077316</v>
+        <v>0.1564113769391631</v>
       </c>
       <c r="E3" s="4">
-        <v>81.20842201911437</v>
+        <v>78.5463878803054</v>
       </c>
       <c r="F3" s="4">
-        <v>84.50700649181236</v>
+        <v>82.58032417891555</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
         <v>30</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0624354979739704</v>
+      </c>
+      <c r="O3" s="5">
+        <v>126</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3921910899862767</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1694896341653997</v>
+      </c>
+      <c r="R3" s="5">
+        <v>126</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>1.189114499973648</v>
+        <v>0.4545102636349851</v>
       </c>
       <c r="C4" s="4">
-        <v>1.014731497616566</v>
+        <v>0.2155336650992488</v>
       </c>
       <c r="D4" s="4">
-        <v>1.405500253975932</v>
+        <v>0.217164744968518</v>
       </c>
       <c r="E4" s="4">
-        <v>83.68438733518134</v>
+        <v>80.75480809607805</v>
       </c>
       <c r="F4" s="4">
-        <v>87.59998066672037</v>
+        <v>84.33845665202608</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" s="5">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.06351438904302983</v>
+      </c>
+      <c r="O4" s="5">
+        <v>127</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4473605009153394</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2141719439069304</v>
+      </c>
+      <c r="R4" s="5">
+        <v>127</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2844,6 +3280,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2851,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2862,9 +3299,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2898,8 +3341,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2921,91 +3372,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.665488216571923</v>
+        <v>0.373279281509418</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5815155726865189</v>
+        <v>0.1944698319512345</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6386785521244459</v>
+        <v>0.194933532753765</v>
       </c>
       <c r="E3" s="4">
-        <v>82.24719335587011</v>
+        <v>77.11468636534357</v>
       </c>
       <c r="F3" s="4">
-        <v>85.22618410397864</v>
+        <v>79.60081525095676</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I3" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J3" s="5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L3" s="5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0183582872927131</v>
+      </c>
+      <c r="O3" s="5">
+        <v>124</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3709897871757808</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1931658273444513</v>
+      </c>
+      <c r="R3" s="5">
+        <v>124</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6190698287496942</v>
+        <v>0.491991344489324</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5012589844361673</v>
+        <v>0.2176778804907421</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5660992726520615</v>
+        <v>0.2225699824050865</v>
       </c>
       <c r="E4" s="4">
-        <v>84.22776518014678</v>
+        <v>78.69383555891503</v>
       </c>
       <c r="F4" s="4">
-        <v>87.13563675532099</v>
+        <v>81.98739194078576</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.002735157806893578</v>
+      </c>
+      <c r="O4" s="5">
+        <v>124</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4923695477769165</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2178190611978364</v>
+      </c>
+      <c r="R4" s="5">
+        <v>124</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3016,6 +3521,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3023,7 +3529,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3034,9 +3540,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -3070,8 +3582,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3093,91 +3613,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4027896380587037</v>
+        <v>1.378798811061967</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2271335302414071</v>
+        <v>1.090417123643917</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2066957326268223</v>
+        <v>1.459599411077316</v>
       </c>
       <c r="E3" s="4">
-        <v>74.61458202913084</v>
+        <v>81.20842201911437</v>
       </c>
       <c r="F3" s="4">
-        <v>79.18920959086527</v>
+        <v>84.50700649181236</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I3" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K3" s="5">
         <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.200557002704291</v>
+      </c>
+      <c r="O3" s="5">
+        <v>135</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4456577696602528</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.275003615172237</v>
+      </c>
+      <c r="R3" s="5">
+        <v>135</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3625682753477815</v>
+        <v>1.189114499973648</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2416491955963435</v>
+        <v>1.014731497616566</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2446277528704328</v>
+        <v>1.405500253975932</v>
       </c>
       <c r="E4" s="4">
-        <v>77.06202233980048</v>
+        <v>83.68438733518134</v>
       </c>
       <c r="F4" s="4">
-        <v>81.91440881597238</v>
+        <v>87.59998066672037</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" s="5">
         <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.119422946455911</v>
+      </c>
+      <c r="O4" s="5">
+        <v>143</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3817522441362974</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2910422427626776</v>
+      </c>
+      <c r="R4" s="5">
+        <v>142</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3188,6 +3762,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3195,7 +3770,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3206,9 +3781,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -3242,8 +3823,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3265,91 +3854,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.236682402652174</v>
+        <v>0.665488216571923</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1666144048425437</v>
+        <v>0.5815155726865189</v>
       </c>
       <c r="D3" s="4">
-        <v>0.167430715716229</v>
+        <v>0.6386785521244459</v>
       </c>
       <c r="E3" s="4">
-        <v>85.16735528567277</v>
+        <v>82.24719335587011</v>
       </c>
       <c r="F3" s="4">
-        <v>88.11394298733209</v>
+        <v>85.22618410397864</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="I3" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5815155726865189</v>
+      </c>
+      <c r="O3" s="5">
+        <v>133</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2862094933059399</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1794227422540648</v>
+      </c>
+      <c r="R3" s="5">
+        <v>133</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3217821450417134</v>
+        <v>0.6190698287496942</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2070379066525683</v>
+        <v>0.5012589844361673</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2190197990410377</v>
+        <v>0.5660992726520615</v>
       </c>
       <c r="E4" s="4">
-        <v>86.3235911648617</v>
+        <v>84.22776518014678</v>
       </c>
       <c r="F4" s="4">
-        <v>89.18454994890351</v>
+        <v>87.13563675532099</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.471220578172212</v>
+      </c>
+      <c r="O4" s="5">
+        <v>141</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3495941968161407</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2140005052484301</v>
+      </c>
+      <c r="R4" s="5">
+        <v>141</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3360,6 +4003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3367,7 +4011,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3378,9 +4022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -3414,8 +4064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3437,66 +4095,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4750347063244826</v>
+        <v>0.4027896380587037</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2722764193898721</v>
+        <v>0.2271335302414071</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2731800631370421</v>
+        <v>0.2066957326268223</v>
       </c>
       <c r="E3" s="4">
-        <v>76.74262342974032</v>
+        <v>74.61458202913084</v>
       </c>
       <c r="F3" s="4">
-        <v>81.35600664278486</v>
+        <v>79.18920959086527</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I3" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K3" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03234064489345963</v>
+      </c>
+      <c r="O3" s="5">
+        <v>123</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4054720155905449</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.227033639917773</v>
+      </c>
+      <c r="R3" s="5">
+        <v>123</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3944219088421089</v>
+        <v>0.3625682753477815</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2066120141735072</v>
+        <v>0.2416491955963435</v>
       </c>
       <c r="D4" s="4">
-        <v>0.217758937510504</v>
+        <v>0.2446277528704328</v>
       </c>
       <c r="E4" s="4">
-        <v>77.80066347526656</v>
+        <v>77.06202233980048</v>
       </c>
       <c r="F4" s="4">
-        <v>82.62483773855726</v>
+        <v>81.91440881597238</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
@@ -3505,23 +4199,41 @@
         <v>130</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K4" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.06450292130936837</v>
+      </c>
+      <c r="O4" s="5">
+        <v>130</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3572588219461229</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.236618138055063</v>
+      </c>
+      <c r="R4" s="5">
+        <v>130</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3532,12 +4244,3198 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>85.53846153846155</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.692307692307693</v>
+      </c>
+      <c r="D3" s="3">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.846153846153846</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.923076923076923</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4125596800163958</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3245531226974979</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3118026646396163</v>
+      </c>
+      <c r="K3" s="4">
+        <v>81.24374672946142</v>
+      </c>
+      <c r="L3" s="4">
+        <v>85.26769919118939</v>
+      </c>
+      <c r="M3" s="5">
+        <v>325</v>
+      </c>
+      <c r="N3" s="5">
+        <v>855627.9256343842</v>
+      </c>
+      <c r="O3" s="4">
+        <v>18.15232360901188</v>
+      </c>
+      <c r="P3" s="5">
+        <v>47136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>68</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="D4" s="3">
+        <v>25.84615384615385</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9.846153846153847</v>
+      </c>
+      <c r="F4" s="3">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5161935213117174</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2343811402111224</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2206438143133774</v>
+      </c>
+      <c r="K4" s="4">
+        <v>70.47619047619058</v>
+      </c>
+      <c r="L4" s="4">
+        <v>76.15852693168139</v>
+      </c>
+      <c r="M4" s="5">
+        <v>325</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4192900.455713272</v>
+      </c>
+      <c r="O4" s="4">
+        <v>33.91930085357057</v>
+      </c>
+      <c r="P4" s="5">
+        <v>123614</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>80</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="D5" s="3">
+        <v>14.46153846153846</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="F5" s="3">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3425569364955162</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2880587202447968</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2618454215240972</v>
+      </c>
+      <c r="K5" s="4">
+        <v>75.90570381998941</v>
+      </c>
+      <c r="L5" s="4">
+        <v>80.50635002581365</v>
+      </c>
+      <c r="M5" s="5">
+        <v>325</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2629788.564443588</v>
+      </c>
+      <c r="O5" s="4">
+        <v>45.31774193423382</v>
+      </c>
+      <c r="P5" s="5">
+        <v>58030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12.61538461538461</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>8.615384615384615</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3472870623814636</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1895734726551952</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1980478636223638</v>
+      </c>
+      <c r="K6" s="4">
+        <v>80.16389324960744</v>
+      </c>
+      <c r="L6" s="4">
+        <v>84.36475649629999</v>
+      </c>
+      <c r="M6" s="5">
+        <v>325</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8470603.838443756</v>
+      </c>
+      <c r="O6" s="4">
+        <v>135.1102791087465</v>
+      </c>
+      <c r="P6" s="5">
+        <v>62694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>75.38461538461539</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="D7" s="3">
+        <v>19.07692307692308</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4.307692307692307</v>
+      </c>
+      <c r="F7" s="3">
+        <v>14.76923076923077</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3742973928955854</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2029138239907534</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2069638460689036</v>
+      </c>
+      <c r="K7" s="4">
+        <v>74.71491365777081</v>
+      </c>
+      <c r="L7" s="4">
+        <v>80.24742729306506</v>
+      </c>
+      <c r="M7" s="5">
+        <v>325</v>
+      </c>
+      <c r="N7" s="5">
+        <v>6892472.770452499</v>
+      </c>
+      <c r="O7" s="4">
+        <v>87.53457925390525</v>
+      </c>
+      <c r="P7" s="5">
+        <v>78740</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>86.46153846153845</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7.384615384615385</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2086615161298528</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.130040003663037</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.134704887756687</v>
+      </c>
+      <c r="K8" s="4">
+        <v>85.51585557299833</v>
+      </c>
+      <c r="L8" s="4">
+        <v>88.44223025296849</v>
+      </c>
+      <c r="M8" s="5">
+        <v>325</v>
+      </c>
+      <c r="N8" s="5">
+        <v>8520227.988004684</v>
+      </c>
+      <c r="O8" s="4">
+        <v>160.232970775279</v>
+      </c>
+      <c r="P8" s="5">
+        <v>53174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75.07692307692308</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.461538461538462</v>
+      </c>
+      <c r="D9" s="3">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15.07692307692308</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3561000285941734</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.223588941374435</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.219994999149419</v>
+      </c>
+      <c r="K9" s="4">
+        <v>78.08592360020928</v>
+      </c>
+      <c r="L9" s="4">
+        <v>81.89568060574778</v>
+      </c>
+      <c r="M9" s="5">
+        <v>325</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1465264.305591583</v>
+      </c>
+      <c r="O9" s="4">
+        <v>12.83630578704847</v>
+      </c>
+      <c r="P9" s="5">
+        <v>114150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>78.76923076923077</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.846153846153846</v>
+      </c>
+      <c r="D10" s="3">
+        <v>19.38461538461538</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="F10" s="3">
+        <v>11.07692307692308</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.618432285839026</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2440870956422226</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2644554363629044</v>
+      </c>
+      <c r="K10" s="4">
+        <v>75.47901622187327</v>
+      </c>
+      <c r="L10" s="4">
+        <v>80.05992083978667</v>
+      </c>
+      <c r="M10" s="5">
+        <v>325</v>
+      </c>
+      <c r="N10" s="5">
+        <v>7614875.867128372</v>
+      </c>
+      <c r="O10" s="4">
+        <v>60.86495885356501</v>
+      </c>
+      <c r="P10" s="5">
+        <v>125111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>85.84615384615385</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="D11" s="3">
+        <v>11.07692307692308</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="F11" s="3">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3434663151935653</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1957369283388323</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1878676954805992</v>
+      </c>
+      <c r="K11" s="4">
+        <v>81.34160125588707</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.28762691447251</v>
+      </c>
+      <c r="M11" s="5">
+        <v>325</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3456411.633014679</v>
+      </c>
+      <c r="O11" s="4">
+        <v>59.01334527940377</v>
+      </c>
+      <c r="P11" s="5">
+        <v>58570</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>71.07692307692308</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.923076923076923</v>
+      </c>
+      <c r="D12" s="3">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.538461538461538</v>
+      </c>
+      <c r="F12" s="3">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4786132976025657</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2637951150748996</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.246277270161654</v>
+      </c>
+      <c r="K12" s="4">
+        <v>71.51669283097867</v>
+      </c>
+      <c r="L12" s="4">
+        <v>77.24804680777817</v>
+      </c>
+      <c r="M12" s="5">
+        <v>325</v>
+      </c>
+      <c r="N12" s="5">
+        <v>6240330.505371094</v>
+      </c>
+      <c r="O12" s="4">
+        <v>60.6634765463613</v>
+      </c>
+      <c r="P12" s="5">
+        <v>102868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>77.84615384615384</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4</v>
+      </c>
+      <c r="D13" s="3">
+        <v>18.15384615384615</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7.384615384615385</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10.76923076923077</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4196909194339942</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1919190939961286</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1887564685955366</v>
+      </c>
+      <c r="K13" s="4">
+        <v>79.64720041862915</v>
+      </c>
+      <c r="L13" s="4">
+        <v>83.45668559628368</v>
+      </c>
+      <c r="M13" s="5">
+        <v>325</v>
+      </c>
+      <c r="N13" s="5">
+        <v>9603457.632780075</v>
+      </c>
+      <c r="O13" s="4">
+        <v>92.85521380704745</v>
+      </c>
+      <c r="P13" s="5">
+        <v>103424</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>76.30769230769231</v>
+      </c>
+      <c r="C14" s="3">
+        <v>5.230769230769231</v>
+      </c>
+      <c r="D14" s="3">
+        <v>18.46153846153846</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.461538461538462</v>
+      </c>
+      <c r="F14" s="3">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.4314929293831161</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2054924442711439</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2095251899044001</v>
+      </c>
+      <c r="K14" s="4">
+        <v>77.90183150183165</v>
+      </c>
+      <c r="L14" s="4">
+        <v>80.79043193942559</v>
+      </c>
+      <c r="M14" s="5">
+        <v>325</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3539883.114099503</v>
+      </c>
+      <c r="O14" s="4">
+        <v>41.37214083471053</v>
+      </c>
+      <c r="P14" s="5">
+        <v>85562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>85.23076923076923</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="D15" s="3">
+        <v>11.38461538461539</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7.076923076923077</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4138033230913889</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2832255831066867</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3329161074322894</v>
+      </c>
+      <c r="K15" s="4">
+        <v>82.44259549973845</v>
+      </c>
+      <c r="L15" s="4">
+        <v>86.0487351574596</v>
+      </c>
+      <c r="M15" s="5">
+        <v>325</v>
+      </c>
+      <c r="N15" s="5">
+        <v>386749.7234344482</v>
+      </c>
+      <c r="O15" s="4">
+        <v>6.827244093956507</v>
+      </c>
+      <c r="P15" s="5">
+        <v>56648</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>84.30769230769231</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4.307692307692307</v>
+      </c>
+      <c r="D16" s="3">
+        <v>11.38461538461539</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7.384615384615385</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3178043301325631</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.197216408612479</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.201508847468796</v>
+      </c>
+      <c r="K16" s="4">
+        <v>83.23443223443243</v>
+      </c>
+      <c r="L16" s="4">
+        <v>86.1779728101874</v>
+      </c>
+      <c r="M16" s="5">
+        <v>325</v>
+      </c>
+      <c r="N16" s="5">
+        <v>650087.0826244354</v>
+      </c>
+      <c r="O16" s="4">
+        <v>11.2686268438973</v>
+      </c>
+      <c r="P16" s="5">
+        <v>57690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>77.84615384615384</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.230769230769231</v>
+      </c>
+      <c r="D17" s="3">
+        <v>16.92307692307692</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>12.92307692307692</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3814395929124022</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2319584808578825</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2221489429279053</v>
+      </c>
+      <c r="K17" s="4">
+        <v>75.83453689167965</v>
+      </c>
+      <c r="L17" s="4">
+        <v>80.54761658922764</v>
+      </c>
+      <c r="M17" s="5">
+        <v>325</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1288668.076515198</v>
+      </c>
+      <c r="O17" s="4">
+        <v>16.98498868494152</v>
+      </c>
+      <c r="P17" s="5">
+        <v>75871</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>90.76923076923077</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.769230769230769</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2.153846153846154</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4.307692307692307</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.2576246017923318</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.1644159293920417</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.1691390060296277</v>
+      </c>
+      <c r="K18" s="4">
+        <v>85.74369440083737</v>
+      </c>
+      <c r="L18" s="4">
+        <v>88.64759938048515</v>
+      </c>
+      <c r="M18" s="5">
+        <v>325</v>
+      </c>
+      <c r="N18" s="5">
+        <v>701173.5091209412</v>
+      </c>
+      <c r="O18" s="4">
+        <v>18.35917231674019</v>
+      </c>
+      <c r="P18" s="5">
+        <v>38192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="3">
+        <v>79.69230769230769</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.692307692307693</v>
+      </c>
+      <c r="D19" s="3">
+        <v>16.61538461538462</v>
+      </c>
+      <c r="E19" s="3">
+        <v>8</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.615384615384615</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.3809474344195742</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.1858671024960618</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.1863604099511847</v>
+      </c>
+      <c r="K19" s="4">
+        <v>77.27001569858737</v>
+      </c>
+      <c r="L19" s="4">
+        <v>81.9884701428329</v>
+      </c>
+      <c r="M19" s="5">
+        <v>325</v>
+      </c>
+      <c r="N19" s="5">
+        <v>9100794.110298157</v>
+      </c>
+      <c r="O19" s="4">
+        <v>75.83615911119574</v>
+      </c>
+      <c r="P19" s="5">
+        <v>120006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3">
+        <v>84.30769230769231</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3.692307692307693</v>
+      </c>
+      <c r="D20" s="3">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5.846153846153846</v>
+      </c>
+      <c r="F20" s="3">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.3132619815923943</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.1899068012168525</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.1834285612948555</v>
+      </c>
+      <c r="K20" s="4">
+        <v>82.66666666666679</v>
+      </c>
+      <c r="L20" s="4">
+        <v>86.38313543279865</v>
+      </c>
+      <c r="M20" s="5">
+        <v>325</v>
+      </c>
+      <c r="N20" s="5">
+        <v>5874303.419113159</v>
+      </c>
+      <c r="O20" s="4">
+        <v>86.26629589710198</v>
+      </c>
+      <c r="P20" s="5">
+        <v>68095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3">
+        <v>64</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4.923076923076923</v>
+      </c>
+      <c r="D21" s="3">
+        <v>31.07692307692307</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8.923076923076923</v>
+      </c>
+      <c r="F21" s="3">
+        <v>21.84615384615385</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.7401082398251411</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.2496140927409333</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.4166953105892792</v>
+      </c>
+      <c r="K21" s="4">
+        <v>63.17844060701196</v>
+      </c>
+      <c r="L21" s="4">
+        <v>70.86797453106203</v>
+      </c>
+      <c r="M21" s="5">
+        <v>325</v>
+      </c>
+      <c r="N21" s="5">
+        <v>20284779.10375595</v>
+      </c>
+      <c r="O21" s="4">
+        <v>160.1982191525706</v>
+      </c>
+      <c r="P21" s="5">
+        <v>126623</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="3">
+        <v>87.38461538461539</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="D22" s="3">
+        <v>10.15384615384615</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7.384615384615385</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.3131049934382497</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.1451969747908615</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.2806006258224383</v>
+      </c>
+      <c r="K22" s="4">
+        <v>86.97624280481449</v>
+      </c>
+      <c r="L22" s="4">
+        <v>89.34785751161607</v>
+      </c>
+      <c r="M22" s="5">
+        <v>325</v>
+      </c>
+      <c r="N22" s="5">
+        <v>9425951.847314835</v>
+      </c>
+      <c r="O22" s="4">
+        <v>226.4873815972616</v>
+      </c>
+      <c r="P22" s="5">
+        <v>41618</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3">
+        <v>47.69230769230769</v>
+      </c>
+      <c r="C23" s="3">
+        <v>4.923076923076923</v>
+      </c>
+      <c r="D23" s="3">
+        <v>47.38461538461539</v>
+      </c>
+      <c r="E23" s="3">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="F23" s="3">
+        <v>34.46153846153846</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.9876066861938452</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.2695408825334226</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.4762095147727832</v>
+      </c>
+      <c r="K23" s="4">
+        <v>51.79392987964418</v>
+      </c>
+      <c r="L23" s="4">
+        <v>60.37700912063319</v>
+      </c>
+      <c r="M23" s="5">
+        <v>325</v>
+      </c>
+      <c r="N23" s="5">
+        <v>16253589.20526505</v>
+      </c>
+      <c r="O23" s="4">
+        <v>91.43558283789967</v>
+      </c>
+      <c r="P23" s="5">
+        <v>177760</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3">
+        <v>85.23076923076923</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="F24" s="3">
+        <v>8.923076923076923</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.2539374515673265</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.1529264205760139</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.1874922639116891</v>
+      </c>
+      <c r="K24" s="4">
+        <v>85.11261119832555</v>
+      </c>
+      <c r="L24" s="4">
+        <v>87.61462743073459</v>
+      </c>
+      <c r="M24" s="5">
+        <v>325</v>
+      </c>
+      <c r="N24" s="5">
+        <v>4957560.059309006</v>
+      </c>
+      <c r="O24" s="4">
+        <v>100.136544786883</v>
+      </c>
+      <c r="P24" s="5">
+        <v>49508</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="25" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3">
+        <v>85.84615384615385</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2.153846153846154</v>
+      </c>
+      <c r="D25" s="3">
+        <v>12</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="F25" s="3">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H25" s="4">
+        <v>0.3133186982878093</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.2419718213886315</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.2571419152927938</v>
+      </c>
+      <c r="K25" s="4">
+        <v>85.04594453165886</v>
+      </c>
+      <c r="L25" s="4">
+        <v>88.66546205472285</v>
+      </c>
+      <c r="M25" s="5">
+        <v>325</v>
+      </c>
+      <c r="N25" s="5">
+        <v>4600856.693506241</v>
+      </c>
+      <c r="O25" s="4">
+        <v>88.36246242425752</v>
+      </c>
+      <c r="P25" s="5">
+        <v>52068</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.236682402652174</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1666144048425437</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.167430715716229</v>
+      </c>
+      <c r="E3" s="4">
+        <v>85.16735528567277</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.11394298733209</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>146</v>
+      </c>
+      <c r="I3" s="5">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5">
+        <v>10</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>8</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.08987090723391628</v>
+      </c>
+      <c r="O3" s="5">
+        <v>146</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2154349022235531</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1430590108607807</v>
+      </c>
+      <c r="R3" s="5">
+        <v>146</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3217821450417134</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2070379066525683</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2190197990410377</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.3235911648617</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.18454994890351</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>149</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>12</v>
+      </c>
+      <c r="K4" s="5">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.103788506748059</v>
+      </c>
+      <c r="O4" s="5">
+        <v>150</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.300074731605362</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1853428428522035</v>
+      </c>
+      <c r="R4" s="5">
+        <v>149</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4750347063244826</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2722764193898721</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2731800631370421</v>
+      </c>
+      <c r="E3" s="4">
+        <v>76.74262342974032</v>
+      </c>
+      <c r="F3" s="4">
+        <v>81.35600664278486</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>129</v>
+      </c>
+      <c r="I3" s="5">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5">
+        <v>24</v>
+      </c>
+      <c r="K3" s="5">
+        <v>11</v>
+      </c>
+      <c r="L3" s="5">
+        <v>13</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2386808447308738</v>
+      </c>
+      <c r="O3" s="5">
+        <v>129</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3782744017457666</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.174355489515992</v>
+      </c>
+      <c r="R3" s="5">
+        <v>129</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3944219088421089</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2066120141735072</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.217758937510504</v>
+      </c>
+      <c r="E4" s="4">
+        <v>77.80066347526656</v>
+      </c>
+      <c r="F4" s="4">
+        <v>82.62483773855726</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>130</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>30</v>
+      </c>
+      <c r="K4" s="5">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.05233378975132903</v>
+      </c>
+      <c r="O4" s="5">
+        <v>130</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3836369672950721</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.197290164607054</v>
+      </c>
+      <c r="R4" s="5">
+        <v>130</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3161622762474914</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1672374403745635</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1519411649488278</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.47907015566976</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.06999629431317</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>133</v>
+      </c>
+      <c r="I3" s="5">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5">
+        <v>11</v>
+      </c>
+      <c r="L3" s="5">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.05731164827214132</v>
+      </c>
+      <c r="O3" s="5">
+        <v>133</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3168204008139716</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1731668260222488</v>
+      </c>
+      <c r="R3" s="5">
+        <v>133</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3116686013101608</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2056332873351612</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2111734101743943</v>
+      </c>
+      <c r="E4" s="4">
+        <v>83.86159402032388</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.70438036843571</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>141</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>19</v>
+      </c>
+      <c r="K4" s="5">
+        <v>8</v>
+      </c>
+      <c r="L4" s="5">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.06004697269541207</v>
+      </c>
+      <c r="O4" s="5">
+        <v>141</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3096815968200665</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2056969905848122</v>
+      </c>
+      <c r="R4" s="5">
+        <v>141</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5424037762613715</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2477553587481101</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.334207428850602</v>
+      </c>
+      <c r="E3" s="4">
+        <v>63.21543341262881</v>
+      </c>
+      <c r="F3" s="4">
+        <v>71.84749042697679</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>110</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>48</v>
+      </c>
+      <c r="K3" s="5">
+        <v>10</v>
+      </c>
+      <c r="L3" s="5">
+        <v>38</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1628822943787176</v>
+      </c>
+      <c r="O3" s="5">
+        <v>110</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4929198543541833</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1543223708952885</v>
+      </c>
+      <c r="R3" s="5">
+        <v>110</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.97986632172578</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4671878833328733</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6808208780703987</v>
+      </c>
+      <c r="E4" s="4">
+        <v>63.14121945074321</v>
+      </c>
+      <c r="F4" s="4">
+        <v>69.88241224072691</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>99</v>
+      </c>
+      <c r="I4" s="5">
+        <v>11</v>
+      </c>
+      <c r="J4" s="5">
+        <v>52</v>
+      </c>
+      <c r="K4" s="5">
+        <v>19</v>
+      </c>
+      <c r="L4" s="5">
+        <v>33</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3143797344637121</v>
+      </c>
+      <c r="O4" s="5">
+        <v>99</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9888224795274009</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3565741886901265</v>
+      </c>
+      <c r="R4" s="5">
+        <v>98</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5622485936770365</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.445739483075179</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4485933064354561</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.87679979967413</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.42211882900288</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>141</v>
+      </c>
+      <c r="I3" s="5">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>13</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4392626978035036</v>
+      </c>
+      <c r="O3" s="5">
+        <v>141</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2665921198403519</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1283850132848333</v>
+      </c>
+      <c r="R3" s="5">
+        <v>141</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5289846144200565</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3393744483482251</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6009341027738787</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.07629965566555</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.27313779103267</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>143</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="5">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3113076583162423</v>
+      </c>
+      <c r="O4" s="5">
+        <v>143</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3599049835398382</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1617738039681342</v>
+      </c>
+      <c r="R4" s="5">
+        <v>143</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7421660394017255</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4412640523539432</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4943559565228279</v>
+      </c>
+      <c r="E3" s="4">
+        <v>52.99194524435549</v>
+      </c>
+      <c r="F3" s="4">
+        <v>62.38701088373808</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>90</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>68</v>
+      </c>
+      <c r="K3" s="5">
+        <v>16</v>
+      </c>
+      <c r="L3" s="5">
+        <v>52</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4162763209220244</v>
+      </c>
+      <c r="O3" s="5">
+        <v>90</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6303684668056216</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1718441852404744</v>
+      </c>
+      <c r="R3" s="5">
+        <v>90</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.277245162293263</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5967537580060203</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7836059310864412</v>
+      </c>
+      <c r="E4" s="4">
+        <v>50.58851935836068</v>
+      </c>
+      <c r="F4" s="4">
+        <v>58.35459993923887</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>67</v>
+      </c>
+      <c r="I4" s="5">
+        <v>11</v>
+      </c>
+      <c r="J4" s="5">
+        <v>84</v>
+      </c>
+      <c r="K4" s="5">
+        <v>24</v>
+      </c>
+      <c r="L4" s="5">
+        <v>60</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4149701450443926</v>
+      </c>
+      <c r="O4" s="5">
+        <v>67</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.347050079775823</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4048132326313509</v>
+      </c>
+      <c r="R4" s="5">
+        <v>65</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3338323781832672</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2956131555495771</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3007238284689445</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.85726806059809</v>
+      </c>
+      <c r="F3" s="4">
+        <v>87.51986659529751</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>136</v>
+      </c>
+      <c r="I3" s="5">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2870719996060959</v>
+      </c>
+      <c r="O3" s="5">
+        <v>136</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1731668059535966</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1227870378018083</v>
+      </c>
+      <c r="R3" s="5">
+        <v>136</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4882390738463379</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3385729084614459</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3943339635785363</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.36953052826117</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.7099732095981</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>141</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>20</v>
+      </c>
+      <c r="K4" s="5">
+        <v>7</v>
+      </c>
+      <c r="L4" s="5">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3078994064678701</v>
+      </c>
+      <c r="O4" s="5">
+        <v>141</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3352066814132399</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1819970309114178</v>
+      </c>
+      <c r="R4" s="5">
+        <v>141</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.270424491129922</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.140956479454121</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.245810902641471</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.58182045824456</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.45287602421045</v>
+      </c>
+      <c r="G3" s="5">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>128</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.248864851469947</v>
+      </c>
+      <c r="O3" s="5">
+        <v>139</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2923312255999326</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2388376193747755</v>
+      </c>
+      <c r="R3" s="5">
+        <v>138</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.9700644441325037</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.8761086191261956</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.9417399468905406</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.51293356848925</v>
+      </c>
+      <c r="F4" s="4">
+        <v>88.87936034468315</v>
+      </c>
+      <c r="G4" s="5">
+        <v>162</v>
+      </c>
+      <c r="H4" s="5">
+        <v>138</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>22</v>
+      </c>
+      <c r="K4" s="5">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5">
+        <v>14</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.9099076630468238</v>
+      </c>
+      <c r="O4" s="5">
+        <v>141</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3344357232762284</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2450393382532565</v>
+      </c>
+      <c r="R4" s="5">
+        <v>141</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3651,16 +7549,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3695,16 +7593,16 @@
         <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="M4" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3739,16 +7637,16 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3783,16 +7681,16 @@
         <v>4</v>
       </c>
       <c r="K6" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3827,16 +7725,16 @@
         <v>4</v>
       </c>
       <c r="K7" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3871,16 +7769,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3915,16 +7813,16 @@
         <v>3</v>
       </c>
       <c r="K9" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L9" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M9" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3959,16 +7857,16 @@
         <v>5</v>
       </c>
       <c r="K10" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="M10" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N10" s="5">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -4003,16 +7901,16 @@
         <v>2</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -4047,16 +7945,16 @@
         <v>8</v>
       </c>
       <c r="K12" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="M12" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -4091,16 +7989,16 @@
         <v>8</v>
       </c>
       <c r="K13" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="M13" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N13" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -4135,16 +8033,16 @@
         <v>6</v>
       </c>
       <c r="K14" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="M14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -4179,16 +8077,16 @@
         <v>1</v>
       </c>
       <c r="K15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -4223,16 +8121,16 @@
         <v>4</v>
       </c>
       <c r="K16" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -4267,16 +8165,16 @@
         <v>5</v>
       </c>
       <c r="K17" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="25" customHeight="1">
@@ -4314,13 +8212,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M18" s="5">
         <v>0</v>
       </c>
       <c r="N18" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="25" customHeight="1">
@@ -4355,16 +8253,16 @@
         <v>9</v>
       </c>
       <c r="K19" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L19" s="5">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="M19" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N19" s="5">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="25" customHeight="1">
@@ -4399,16 +8297,16 @@
         <v>4</v>
       </c>
       <c r="K20" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M20" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="5">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="25" customHeight="1">
@@ -4443,16 +8341,16 @@
         <v>12</v>
       </c>
       <c r="K21" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="M21" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N21" s="5">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="25" customHeight="1">
@@ -4487,16 +8385,16 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M22" s="5">
         <v>0</v>
       </c>
       <c r="N22" s="5">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="25" customHeight="1">
@@ -4531,16 +8429,16 @@
         <v>13</v>
       </c>
       <c r="K23" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="M23" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N23" s="5">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="25" customHeight="1">
@@ -4575,16 +8473,16 @@
         <v>3</v>
       </c>
       <c r="K24" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M24" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N24" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="25" customHeight="1">
@@ -4619,16 +8517,16 @@
         <v>2</v>
       </c>
       <c r="K25" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M25" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4644,9 +8542,1116 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>278</v>
+      </c>
+      <c r="C3" s="5">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5">
+        <v>29</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>20</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>221</v>
+      </c>
+      <c r="C4" s="5">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
+        <v>84</v>
+      </c>
+      <c r="E4" s="5">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5">
+        <v>52</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5">
+        <v>28</v>
+      </c>
+      <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>33</v>
+      </c>
+      <c r="M4" s="5">
+        <v>9</v>
+      </c>
+      <c r="N4" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>260</v>
+      </c>
+      <c r="C5" s="5">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5">
+        <v>47</v>
+      </c>
+      <c r="E5" s="5">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>8</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>29</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>275</v>
+      </c>
+      <c r="C6" s="5">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5">
+        <v>13</v>
+      </c>
+      <c r="F6" s="5">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5">
+        <v>11</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>21</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>245</v>
+      </c>
+      <c r="C7" s="5">
+        <v>18</v>
+      </c>
+      <c r="D7" s="5">
+        <v>62</v>
+      </c>
+      <c r="E7" s="5">
+        <v>14</v>
+      </c>
+      <c r="F7" s="5">
+        <v>48</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5">
+        <v>11</v>
+      </c>
+      <c r="J7" s="5">
+        <v>4</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>31</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>281</v>
+      </c>
+      <c r="C8" s="5">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5">
+        <v>11</v>
+      </c>
+      <c r="F8" s="5">
+        <v>24</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>11</v>
+      </c>
+      <c r="I8" s="5">
+        <v>11</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>18</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>244</v>
+      </c>
+      <c r="C9" s="5">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5">
+        <v>60</v>
+      </c>
+      <c r="E9" s="5">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>49</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10</v>
+      </c>
+      <c r="J9" s="5">
+        <v>3</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="5">
+        <v>31</v>
+      </c>
+      <c r="M9" s="5">
+        <v>6</v>
+      </c>
+      <c r="N9" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>256</v>
+      </c>
+      <c r="C10" s="5">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5">
+        <v>63</v>
+      </c>
+      <c r="E10" s="5">
+        <v>25</v>
+      </c>
+      <c r="F10" s="5">
+        <v>36</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>25</v>
+      </c>
+      <c r="I10" s="5">
+        <v>23</v>
+      </c>
+      <c r="J10" s="5">
+        <v>5</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>33</v>
+      </c>
+      <c r="M10" s="5">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>279</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>26</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5">
+        <v>8</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>20</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>231</v>
+      </c>
+      <c r="C12" s="5">
+        <v>16</v>
+      </c>
+      <c r="D12" s="5">
+        <v>78</v>
+      </c>
+      <c r="E12" s="5">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5">
+        <v>60</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>18</v>
+      </c>
+      <c r="I12" s="5">
+        <v>16</v>
+      </c>
+      <c r="J12" s="5">
+        <v>8</v>
+      </c>
+      <c r="K12" s="5">
+        <v>4</v>
+      </c>
+      <c r="L12" s="5">
+        <v>40</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>253</v>
+      </c>
+      <c r="C13" s="5">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5">
+        <v>59</v>
+      </c>
+      <c r="E13" s="5">
+        <v>24</v>
+      </c>
+      <c r="F13" s="5">
+        <v>35</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>24</v>
+      </c>
+      <c r="I13" s="5">
+        <v>21</v>
+      </c>
+      <c r="J13" s="5">
+        <v>8</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>24</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>248</v>
+      </c>
+      <c r="C14" s="5">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5">
+        <v>60</v>
+      </c>
+      <c r="E14" s="5">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5">
+        <v>39</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>21</v>
+      </c>
+      <c r="I14" s="5">
+        <v>20</v>
+      </c>
+      <c r="J14" s="5">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>27</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>277</v>
+      </c>
+      <c r="C15" s="5">
+        <v>11</v>
+      </c>
+      <c r="D15" s="5">
+        <v>37</v>
+      </c>
+      <c r="E15" s="5">
+        <v>13</v>
+      </c>
+      <c r="F15" s="5">
+        <v>23</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>13</v>
+      </c>
+      <c r="I15" s="5">
+        <v>13</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>15</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>274</v>
+      </c>
+      <c r="C16" s="5">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5">
+        <v>37</v>
+      </c>
+      <c r="E16" s="5">
+        <v>13</v>
+      </c>
+      <c r="F16" s="5">
+        <v>24</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>13</v>
+      </c>
+      <c r="I16" s="5">
+        <v>11</v>
+      </c>
+      <c r="J16" s="5">
+        <v>4</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>15</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>253</v>
+      </c>
+      <c r="C17" s="5">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>55</v>
+      </c>
+      <c r="E17" s="5">
+        <v>13</v>
+      </c>
+      <c r="F17" s="5">
+        <v>42</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>13</v>
+      </c>
+      <c r="I17" s="5">
+        <v>12</v>
+      </c>
+      <c r="J17" s="5">
+        <v>5</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>30</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>295</v>
+      </c>
+      <c r="C18" s="5">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5">
+        <v>22</v>
+      </c>
+      <c r="E18" s="5">
+        <v>7</v>
+      </c>
+      <c r="F18" s="5">
+        <v>14</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5">
+        <v>7</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>11</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5">
+        <v>259</v>
+      </c>
+      <c r="C19" s="5">
+        <v>12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>54</v>
+      </c>
+      <c r="E19" s="5">
+        <v>26</v>
+      </c>
+      <c r="F19" s="5">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>26</v>
+      </c>
+      <c r="I19" s="5">
+        <v>23</v>
+      </c>
+      <c r="J19" s="5">
+        <v>9</v>
+      </c>
+      <c r="K19" s="5">
+        <v>4</v>
+      </c>
+      <c r="L19" s="5">
+        <v>22</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5">
+        <v>274</v>
+      </c>
+      <c r="C20" s="5">
+        <v>12</v>
+      </c>
+      <c r="D20" s="5">
+        <v>39</v>
+      </c>
+      <c r="E20" s="5">
+        <v>19</v>
+      </c>
+      <c r="F20" s="5">
+        <v>20</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>19</v>
+      </c>
+      <c r="I20" s="5">
+        <v>17</v>
+      </c>
+      <c r="J20" s="5">
+        <v>4</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>15</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5">
+        <v>208</v>
+      </c>
+      <c r="C21" s="5">
+        <v>16</v>
+      </c>
+      <c r="D21" s="5">
+        <v>101</v>
+      </c>
+      <c r="E21" s="5">
+        <v>29</v>
+      </c>
+      <c r="F21" s="5">
+        <v>71</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>29</v>
+      </c>
+      <c r="I21" s="5">
+        <v>22</v>
+      </c>
+      <c r="J21" s="5">
+        <v>12</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5">
+        <v>59</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5">
+        <v>284</v>
+      </c>
+      <c r="C22" s="5">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5">
+        <v>33</v>
+      </c>
+      <c r="E22" s="5">
+        <v>9</v>
+      </c>
+      <c r="F22" s="5">
+        <v>24</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>9</v>
+      </c>
+      <c r="I22" s="5">
+        <v>9</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>15</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5">
+        <v>155</v>
+      </c>
+      <c r="C23" s="5">
+        <v>16</v>
+      </c>
+      <c r="D23" s="5">
+        <v>154</v>
+      </c>
+      <c r="E23" s="5">
+        <v>40</v>
+      </c>
+      <c r="F23" s="5">
+        <v>112</v>
+      </c>
+      <c r="G23" s="5">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5">
+        <v>40</v>
+      </c>
+      <c r="I23" s="5">
+        <v>35</v>
+      </c>
+      <c r="J23" s="5">
+        <v>13</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <v>90</v>
+      </c>
+      <c r="M23" s="5">
+        <v>1</v>
+      </c>
+      <c r="N23" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5">
+        <v>277</v>
+      </c>
+      <c r="C24" s="5">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>39</v>
+      </c>
+      <c r="E24" s="5">
+        <v>10</v>
+      </c>
+      <c r="F24" s="5">
+        <v>29</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>10</v>
+      </c>
+      <c r="I24" s="5">
+        <v>8</v>
+      </c>
+      <c r="J24" s="5">
+        <v>3</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>20</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="25" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5">
+        <v>279</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>39</v>
+      </c>
+      <c r="E25" s="5">
+        <v>8</v>
+      </c>
+      <c r="F25" s="5">
+        <v>30</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5">
+        <v>8</v>
+      </c>
+      <c r="I25" s="5">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5">
+        <v>2</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>22</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4657,9 +9662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -4693,8 +9704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4716,91 +9735,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3161622762474914</v>
+        <v>1.442018537895569</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1672374403745635</v>
+        <v>1.225296465820067</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1519411649488278</v>
+        <v>1.365168219243065</v>
       </c>
       <c r="E3" s="4">
-        <v>81.47907015566976</v>
+        <v>80.70155669629816</v>
       </c>
       <c r="F3" s="4">
-        <v>85.06999629431317</v>
+        <v>85.01228366341377</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K3" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>19</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.402179691584727</v>
+      </c>
+      <c r="O3" s="5">
+        <v>137</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4166697305084675</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.355131674855311</v>
+      </c>
+      <c r="R3" s="5">
+        <v>137</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3116686013101608</v>
+        <v>1.161960528733781</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2056332873351612</v>
+        <v>0.9994900620767915</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2111734101743943</v>
+        <v>1.0888605415486</v>
       </c>
       <c r="E4" s="4">
-        <v>83.86159402032388</v>
+        <v>81.78928361468087</v>
       </c>
       <c r="F4" s="4">
-        <v>87.70438036843571</v>
+        <v>85.52469135802262</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
+        <v>134</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>25</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4</v>
+      </c>
+      <c r="L4" s="5">
+        <v>14</v>
+      </c>
+      <c r="M4" s="5">
+        <v>7</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.063663131132687</v>
+      </c>
+      <c r="O4" s="5">
         <v>141</v>
       </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>19</v>
-      </c>
-      <c r="K4" s="5">
-        <v>8</v>
-      </c>
-      <c r="L4" s="5">
-        <v>11</v>
-      </c>
-      <c r="M4" s="5">
+      <c r="P4" s="4">
+        <v>0.4084242588422744</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2948420471966439</v>
+      </c>
+      <c r="R4" s="5">
+        <v>141</v>
+      </c>
+      <c r="S4" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4811,14 +9884,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4829,9 +9903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -4865,8 +9945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4888,91 +9976,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5424037762613715</v>
+        <v>0.4897146773695684</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2477553587481101</v>
+        <v>0.220555605185513</v>
       </c>
       <c r="D3" s="4">
-        <v>0.334207428850602</v>
+        <v>0.1996327887899431</v>
       </c>
       <c r="E3" s="4">
-        <v>63.21543341262881</v>
+        <v>69.58724594132123</v>
       </c>
       <c r="F3" s="4">
-        <v>71.84749042697679</v>
+        <v>75.30935617133905</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J3" s="5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K3" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L3" s="5">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01300060871079523</v>
+      </c>
+      <c r="O3" s="5">
+        <v>107</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4881837800191215</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2203245020392124</v>
+      </c>
+      <c r="R3" s="5">
+        <v>107</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.97986632172578</v>
+        <v>0.5519045470552364</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4671878833328733</v>
+        <v>0.272025320331563</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6808208780703987</v>
+        <v>0.2708096602972507</v>
       </c>
       <c r="E4" s="4">
-        <v>63.14121945074321</v>
+        <v>71.37062232300319</v>
       </c>
       <c r="F4" s="4">
-        <v>69.88241224072691</v>
+        <v>77.01293948684125</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I4" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K4" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L4" s="5">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1157389194321866</v>
+      </c>
+      <c r="O4" s="5">
+        <v>114</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5443761622419219</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2475746514777396</v>
+      </c>
+      <c r="R4" s="5">
+        <v>114</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4983,14 +10125,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5001,9 +10144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -5037,8 +10186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5060,91 +10217,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5622485936770365</v>
+        <v>0.3484548117657856</v>
       </c>
       <c r="C3" s="4">
-        <v>0.445739483075179</v>
+        <v>0.2995782168216341</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4485933064354561</v>
+        <v>0.2713553183656814</v>
       </c>
       <c r="E3" s="4">
-        <v>86.87679979967413</v>
+        <v>75.40419848921169</v>
       </c>
       <c r="F3" s="4">
-        <v>89.42211882900288</v>
+        <v>79.86487970244681</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K3" s="5">
         <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.04084964334964236</v>
+      </c>
+      <c r="O3" s="5">
+        <v>128</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3452880003498512</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2933115155384715</v>
+      </c>
+      <c r="R3" s="5">
+        <v>128</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5289846144200565</v>
+        <v>0.3677880394294142</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3393744483482251</v>
+        <v>0.3169059846955677</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6009341027738787</v>
+        <v>0.3032513927090756</v>
       </c>
       <c r="E4" s="4">
-        <v>87.07629965566555</v>
+        <v>76.41030486268563</v>
       </c>
       <c r="F4" s="4">
-        <v>89.27313779103267</v>
+        <v>81.15178004253309</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1479632107162064</v>
+      </c>
+      <c r="O4" s="5">
+        <v>132</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3398090142223275</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2829651005660822</v>
+      </c>
+      <c r="R4" s="5">
+        <v>132</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5155,14 +10366,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5173,9 +10385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -5209,8 +10427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5232,91 +10458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7421660394017255</v>
+        <v>0.2813514488253412</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4412640523539432</v>
+        <v>0.1996261687110013</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4943559565228279</v>
+        <v>0.1950773078538585</v>
       </c>
       <c r="E3" s="4">
-        <v>52.99194524435549</v>
+        <v>80.0525854513584</v>
       </c>
       <c r="F3" s="4">
-        <v>62.38701088373808</v>
+        <v>84.54653381095632</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="I3" s="5">
         <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="K3" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1313668290281663</v>
+      </c>
+      <c r="O3" s="5">
+        <v>139</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2561117450490174</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.175699041075233</v>
+      </c>
+      <c r="R3" s="5">
+        <v>139</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>1.277245162293263</v>
+        <v>0.4666117266468337</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5967537580060203</v>
+        <v>0.2319847974020779</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7836059310864412</v>
+        <v>0.237565255195657</v>
       </c>
       <c r="E4" s="4">
-        <v>50.58851935836068</v>
+        <v>80.27588813303136</v>
       </c>
       <c r="F4" s="4">
-        <v>58.35459993923887</v>
+        <v>84.18185709945347</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>22</v>
+      </c>
+      <c r="K4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="5">
-        <v>84</v>
-      </c>
-      <c r="K4" s="5">
-        <v>24</v>
-      </c>
       <c r="L4" s="5">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.09750866148062573</v>
+      </c>
+      <c r="O4" s="5">
+        <v>136</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4390251903147274</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2037539578729506</v>
+      </c>
+      <c r="R4" s="5">
+        <v>136</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5327,14 +10607,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5345,9 +10626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -5381,8 +10668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5404,91 +10699,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3338323781832672</v>
+        <v>0.3812349654045197</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2956131555495771</v>
+        <v>0.1866249810729563</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3007238284689445</v>
+        <v>0.1756999526037666</v>
       </c>
       <c r="E3" s="4">
-        <v>84.85726806059809</v>
+        <v>73.80806310254157</v>
       </c>
       <c r="F3" s="4">
-        <v>87.51986659529751</v>
+        <v>78.92336092010756</v>
       </c>
       <c r="G3" s="5">
         <v>163</v>
       </c>
       <c r="H3" s="5">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="I3" s="5">
+        <v>11</v>
+      </c>
+      <c r="J3" s="5">
+        <v>32</v>
+      </c>
+      <c r="K3" s="5">
         <v>8</v>
       </c>
-      <c r="J3" s="5">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
       <c r="L3" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03965597258268876</v>
+      </c>
+      <c r="O3" s="5">
+        <v>120</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3714041152470423</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1800407026538904</v>
+      </c>
+      <c r="R3" s="5">
+        <v>120</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4882390738463379</v>
+        <v>0.3786967035041733</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3385729084614459</v>
+        <v>0.2264018151385261</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3943339635785363</v>
+        <v>0.2435908557277208</v>
       </c>
       <c r="E4" s="4">
-        <v>85.36953052826117</v>
+        <v>75.62736205593382</v>
       </c>
       <c r="F4" s="4">
-        <v>87.7099732095981</v>
+        <v>81.57966691523536</v>
       </c>
       <c r="G4" s="5">
         <v>162</v>
       </c>
       <c r="H4" s="5">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.01342714790855922</v>
+      </c>
+      <c r="O4" s="5">
+        <v>125</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3772085302826998</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2248720204741418</v>
+      </c>
+      <c r="R4" s="5">
+        <v>125</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5499,1382 +10848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.270424491129922</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.140956479454121</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.245810902641471</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.58182045824456</v>
-      </c>
-      <c r="F3" s="4">
-        <v>88.45287602421045</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>128</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5">
-        <v>30</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>16</v>
-      </c>
-      <c r="M3" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9700644441325037</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8761086191261956</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.9417399468905406</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.51293356848925</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.87936034468315</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>138</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>22</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>14</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.442018537895569</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.225296465820067</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.365168219243065</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.70155669629816</v>
-      </c>
-      <c r="F3" s="4">
-        <v>85.01228366341377</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>118</v>
-      </c>
-      <c r="I3" s="5">
-        <v>9</v>
-      </c>
-      <c r="J3" s="5">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>15</v>
-      </c>
-      <c r="M3" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.161960528733781</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.9994900620767915</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.0888605415486</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.78928361468087</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.52469135802262</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>134</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>25</v>
-      </c>
-      <c r="K4" s="5">
-        <v>4</v>
-      </c>
-      <c r="L4" s="5">
-        <v>14</v>
-      </c>
-      <c r="M4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4897146773695684</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.220555605185513</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1996327887899431</v>
-      </c>
-      <c r="E3" s="4">
-        <v>69.58724594132123</v>
-      </c>
-      <c r="F3" s="4">
-        <v>75.30935617133905</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>107</v>
-      </c>
-      <c r="I3" s="5">
-        <v>14</v>
-      </c>
-      <c r="J3" s="5">
-        <v>42</v>
-      </c>
-      <c r="K3" s="5">
-        <v>16</v>
-      </c>
-      <c r="L3" s="5">
-        <v>26</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5519045470552364</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.272025320331563</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2708096602972507</v>
-      </c>
-      <c r="E4" s="4">
-        <v>71.37062232300319</v>
-      </c>
-      <c r="F4" s="4">
-        <v>77.01293948684125</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>114</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>42</v>
-      </c>
-      <c r="K4" s="5">
-        <v>16</v>
-      </c>
-      <c r="L4" s="5">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3484548117657856</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2995782168216341</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2713553183656814</v>
-      </c>
-      <c r="E3" s="4">
-        <v>75.40419848921169</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.86487970244681</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>128</v>
-      </c>
-      <c r="I3" s="5">
-        <v>13</v>
-      </c>
-      <c r="J3" s="5">
-        <v>22</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>19</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3677880394294142</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3169059846955677</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3032513927090756</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.41030486268563</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.15178004253309</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>132</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>25</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>20</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2813514488253412</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1996261687110013</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1950773078538585</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.0525854513584</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.54653381095632</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>139</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>17</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4666117266468337</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2319847974020779</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.237565255195657</v>
-      </c>
-      <c r="E4" s="4">
-        <v>80.27588813303136</v>
-      </c>
-      <c r="F4" s="4">
-        <v>84.18185709945347</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>136</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>22</v>
-      </c>
-      <c r="K4" s="5">
-        <v>11</v>
-      </c>
-      <c r="L4" s="5">
-        <v>11</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3812349654045197</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1866249810729563</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1756999526037666</v>
-      </c>
-      <c r="E3" s="4">
-        <v>73.80806310254157</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.92336092010756</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>120</v>
-      </c>
-      <c r="I3" s="5">
-        <v>11</v>
-      </c>
-      <c r="J3" s="5">
-        <v>32</v>
-      </c>
-      <c r="K3" s="5">
-        <v>8</v>
-      </c>
-      <c r="L3" s="5">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3786967035041733</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2264018151385261</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2435908557277208</v>
-      </c>
-      <c r="E4" s="4">
-        <v>75.62736205593382</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.57966691523536</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>125</v>
-      </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
-      <c r="J4" s="5">
-        <v>30</v>
-      </c>
-      <c r="K4" s="5">
-        <v>6</v>
-      </c>
-      <c r="L4" s="5">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1334796414541707</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1113602338075775</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1124726852400128</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.52522849630607</v>
-      </c>
-      <c r="F3" s="4">
-        <v>88.62464144055073</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>142</v>
-      </c>
-      <c r="I3" s="5">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5">
-        <v>15</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>14</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2914227144717063</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1557206276096344</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1635042643834083</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.50642479213948</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.25869307039834</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>139</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>20</v>
-      </c>
-      <c r="K4" s="5">
-        <v>10</v>
-      </c>
-      <c r="L4" s="5">
-        <v>10</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3375487983527011</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2069333034833312</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2004904754396683</v>
-      </c>
-      <c r="E3" s="4">
-        <v>76.4625850340138</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.09374013532516</v>
-      </c>
-      <c r="G3" s="5">
-        <v>163</v>
-      </c>
-      <c r="H3" s="5">
-        <v>117</v>
-      </c>
-      <c r="I3" s="5">
-        <v>15</v>
-      </c>
-      <c r="J3" s="5">
-        <v>31</v>
-      </c>
-      <c r="K3" s="5">
-        <v>5</v>
-      </c>
-      <c r="L3" s="5">
-        <v>26</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.382396778675601</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2451190038609061</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2364093265442755</v>
-      </c>
-      <c r="E4" s="4">
-        <v>79.71928277483855</v>
-      </c>
-      <c r="F4" s="4">
-        <v>83.70874416549094</v>
-      </c>
-      <c r="G4" s="5">
-        <v>162</v>
-      </c>
-      <c r="H4" s="5">
-        <v>127</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>29</v>
-      </c>
-      <c r="K4" s="5">
-        <v>6</v>
-      </c>
-      <c r="L4" s="5">
-        <v>23</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ComerGeneralized2024.xlsx
+++ b/public/downloads/ComerGeneralized2024.xlsx
@@ -1986,16 +1986,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03692850509497017</v>
+        <v>-0.02514792122802589</v>
       </c>
       <c r="O3" s="5">
         <v>142</v>
       </c>
       <c r="P3" s="4">
-        <v>0.130511472655447</v>
+        <v>0.130080675322318</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1081994266352257</v>
+        <v>0.107635701707127</v>
       </c>
       <c r="R3" s="5">
         <v>142</v>
@@ -2045,16 +2045,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03136983913752948</v>
+        <v>-0.02926924668700792</v>
       </c>
       <c r="O4" s="5">
         <v>139</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2872939672800265</v>
+        <v>0.287337277440006</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1523519600511608</v>
+        <v>0.1523368478752578</v>
       </c>
       <c r="R4" s="5">
         <v>139</v>
@@ -2227,16 +2227,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03638818208920176</v>
+        <v>-0.01907201538692949</v>
       </c>
       <c r="O3" s="5">
         <v>117</v>
       </c>
       <c r="P3" s="4">
-        <v>0.335778405165628</v>
+        <v>0.3362829423562806</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.206954939100602</v>
+        <v>0.206473829942125</v>
       </c>
       <c r="R3" s="5">
         <v>117</v>
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.044521040269076</v>
+        <v>-0.04859118418934827</v>
       </c>
       <c r="O4" s="5">
         <v>127</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3765470941426483</v>
+        <v>0.3764377416976361</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2389131796896986</v>
+        <v>0.2388698358760673</v>
       </c>
       <c r="R4" s="5">
         <v>127</v>
@@ -2468,16 +2468,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04679944285546225</v>
+        <v>0.1110917343440145</v>
       </c>
       <c r="O3" s="5">
         <v>134</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4919916928218739</v>
+        <v>0.4907989182752289</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2324167314832145</v>
+        <v>0.2237114888473836</v>
       </c>
       <c r="R3" s="5">
         <v>133</v>
@@ -2527,16 +2527,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.09982157691023757</v>
+        <v>-0.07856172394229022</v>
       </c>
       <c r="O4" s="5">
         <v>124</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7456533763439384</v>
+        <v>0.7475479923769091</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.256706269895459</v>
+        <v>0.2561179369552383</v>
       </c>
       <c r="R4" s="5">
         <v>123</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06043501542106314</v>
+        <v>-0.0313870081540204</v>
       </c>
       <c r="O3" s="5">
         <v>136</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2660889121994475</v>
+        <v>0.266589583573164</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1759215006019529</v>
+        <v>0.1745702372384221</v>
       </c>
       <c r="R3" s="5">
         <v>136</v>
@@ -2768,16 +2768,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.09154147178202492</v>
+        <v>-0.06894253418928997</v>
       </c>
       <c r="O4" s="5">
         <v>143</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4213213564777702</v>
+        <v>0.42047310316019</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2145823701025778</v>
+        <v>0.2131473082128842</v>
       </c>
       <c r="R4" s="5">
         <v>143</v>
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3953948319280088</v>
+        <v>-0.3713516766023588</v>
       </c>
       <c r="O3" s="5">
         <v>115</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4635009279515714</v>
+        <v>0.4649195962603142</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.261100097042874</v>
+        <v>0.2597657705134365</v>
       </c>
       <c r="R3" s="5">
         <v>115</v>
@@ -3009,16 +3009,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2764046367147363</v>
+        <v>-0.2755477093634369</v>
       </c>
       <c r="O4" s="5">
         <v>116</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4938189534859734</v>
+        <v>0.4938930089360858</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2664669001928559</v>
+        <v>0.266466900192856</v>
       </c>
       <c r="R4" s="5">
         <v>116</v>
@@ -3191,16 +3191,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0624354979739704</v>
+        <v>-0.03344594297795411</v>
       </c>
       <c r="O3" s="5">
         <v>126</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3921910899862767</v>
+        <v>0.3942573804076037</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1694896341653997</v>
+        <v>0.1682514032427332</v>
       </c>
       <c r="R3" s="5">
         <v>126</v>
@@ -3250,16 +3250,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06351438904302983</v>
+        <v>-0.04204764382008186</v>
       </c>
       <c r="O4" s="5">
         <v>127</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4473605009153394</v>
+        <v>0.4486714711127702</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2141719439069304</v>
+        <v>0.2136330293584953</v>
       </c>
       <c r="R4" s="5">
         <v>127</v>
@@ -3432,16 +3432,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0183582872927131</v>
+        <v>-0.02089033346678093</v>
       </c>
       <c r="O3" s="5">
         <v>124</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3709897871757808</v>
+        <v>0.3708106481285359</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1931658273444513</v>
+        <v>0.1931164511299776</v>
       </c>
       <c r="R3" s="5">
         <v>124</v>
@@ -3491,16 +3491,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.002735157806893578</v>
+        <v>-0.007095951472166462</v>
       </c>
       <c r="O4" s="5">
         <v>124</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4923695477769165</v>
+        <v>0.4912157720789629</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2178190611978364</v>
+        <v>0.2175364969285727</v>
       </c>
       <c r="R4" s="5">
         <v>124</v>
@@ -3673,16 +3673,16 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.200557002704291</v>
+        <v>-1.088374756891341</v>
       </c>
       <c r="O3" s="5">
         <v>135</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4456577696602528</v>
+        <v>0.4364524402066181</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.275003615172237</v>
+        <v>0.2549773388632424</v>
       </c>
       <c r="R3" s="5">
         <v>135</v>
@@ -3732,16 +3732,16 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.119422946455911</v>
+        <v>-1.038384718276017</v>
       </c>
       <c r="O4" s="5">
         <v>143</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3817522441362974</v>
+        <v>0.3682703093113792</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2910422427626776</v>
+        <v>0.2763544280151169</v>
       </c>
       <c r="R4" s="5">
         <v>142</v>
@@ -3914,16 +3914,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5815155726865189</v>
+        <v>-0.534467705842502</v>
       </c>
       <c r="O3" s="5">
         <v>133</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2862094933059399</v>
+        <v>0.283658659151521</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1794227422540648</v>
+        <v>0.1742314379339161</v>
       </c>
       <c r="R3" s="5">
         <v>133</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.471220578172212</v>
+        <v>-0.4564988887946981</v>
       </c>
       <c r="O4" s="5">
         <v>141</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3495941968161407</v>
+        <v>0.3489880973028048</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2140005052484301</v>
+        <v>0.2136173630283742</v>
       </c>
       <c r="R4" s="5">
         <v>141</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03234064489345963</v>
+        <v>0.01853849012144337</v>
       </c>
       <c r="O3" s="5">
         <v>123</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4054720155905449</v>
+        <v>0.4040387669572269</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.227033639917773</v>
+        <v>0.2268725027078866</v>
       </c>
       <c r="R3" s="5">
         <v>123</v>
@@ -4214,13 +4214,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06450292130936837</v>
+        <v>0.06494902776245226</v>
       </c>
       <c r="O4" s="5">
         <v>130</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3572588219461229</v>
+        <v>0.3572533144590477</v>
       </c>
       <c r="Q4" s="4">
         <v>0.236618138055063</v>
@@ -4342,13 +4342,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>85.53846153846155</v>
+        <v>84.92307692307692</v>
       </c>
       <c r="C3" s="3">
         <v>3.692307692307693</v>
       </c>
       <c r="D3" s="3">
-        <v>10.76923076923077</v>
+        <v>11.38461538461539</v>
       </c>
       <c r="E3" s="3">
         <v>1.846153846153846</v>
@@ -4357,16 +4357,16 @@
         <v>8.923076923076923</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4125596800163958</v>
+        <v>0.3951592355318408</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3245531226974979</v>
+        <v>0.2909515353701633</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3118026646396163</v>
+        <v>0.291320628824934</v>
       </c>
       <c r="K3" s="4">
         <v>81.24374672946142</v>
@@ -4410,13 +4410,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5161935213117174</v>
+        <v>0.5169478680526588</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2343811402111224</v>
+        <v>0.2343420414923429</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2206438143133774</v>
+        <v>0.2201672654943558</v>
       </c>
       <c r="K4" s="4">
         <v>70.47619047619058</v>
@@ -4460,13 +4460,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3425569364955162</v>
+        <v>0.3427233348293704</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2880587202447968</v>
+        <v>0.2863825811562097</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2618454215240972</v>
+        <v>0.2626697440570207</v>
       </c>
       <c r="K5" s="4">
         <v>75.90570381998941</v>
@@ -4510,13 +4510,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3472870623814636</v>
+        <v>0.3465527048780979</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1895734726551952</v>
+        <v>0.1883500532554909</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1980478636223638</v>
+        <v>0.1968727263380357</v>
       </c>
       <c r="K6" s="4">
         <v>80.16389324960744</v>
@@ -4560,13 +4560,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3742973928955854</v>
+        <v>0.3717096074944192</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2029138239907534</v>
+        <v>0.2013299055026758</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2069638460689036</v>
+        <v>0.2076180399063734</v>
       </c>
       <c r="K7" s="4">
         <v>74.71491365777081</v>
@@ -4610,13 +4610,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2086615161298528</v>
+        <v>0.2084670431471348</v>
       </c>
       <c r="I8" s="4">
-        <v>0.130040003663037</v>
+        <v>0.129747656573213</v>
       </c>
       <c r="J8" s="4">
-        <v>0.134704887756687</v>
+        <v>0.1347617604263033</v>
       </c>
       <c r="K8" s="4">
         <v>85.51585557299833</v>
@@ -4660,13 +4660,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3561000285941734</v>
+        <v>0.356298565412587</v>
       </c>
       <c r="I9" s="4">
-        <v>0.223588941374435</v>
+        <v>0.2233356854897098</v>
       </c>
       <c r="J9" s="4">
-        <v>0.219994999149419</v>
+        <v>0.2187819728513773</v>
       </c>
       <c r="K9" s="4">
         <v>78.08592360020928</v>
@@ -4710,13 +4710,13 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="H10" s="4">
-        <v>0.618432285839026</v>
+        <v>0.618778456750528</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2440870956422226</v>
+        <v>0.2392817744617044</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2644554363629044</v>
+        <v>0.2587182450905346</v>
       </c>
       <c r="K10" s="4">
         <v>75.47901622187327</v>
@@ -4760,13 +4760,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3434663151935653</v>
+        <v>0.3432945994903893</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1957369283388323</v>
+        <v>0.1943427144762288</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1878676954805992</v>
+        <v>0.1863190869158572</v>
       </c>
       <c r="K11" s="4">
         <v>81.34160125588707</v>
@@ -4810,13 +4810,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4786132976025657</v>
+        <v>0.4793617281171604</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2637951150748996</v>
+        <v>0.2631308399628419</v>
       </c>
       <c r="J12" s="4">
-        <v>0.246277270161654</v>
+        <v>0.2451320753827623</v>
       </c>
       <c r="K12" s="4">
         <v>71.51669283097867</v>
@@ -4860,13 +4860,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4196909194339942</v>
+        <v>0.4213807117744867</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1919190939961286</v>
+        <v>0.1910319033087482</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1887564685955366</v>
+        <v>0.1869071315803687</v>
       </c>
       <c r="K13" s="4">
         <v>79.64720041862915</v>
@@ -4910,13 +4910,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.4314929293831161</v>
+        <v>0.430827971451518</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2054924442711439</v>
+        <v>0.2053264740292751</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2095251899044001</v>
+        <v>0.2099133029177541</v>
       </c>
       <c r="K14" s="4">
         <v>77.90183150183165</v>
@@ -4960,13 +4960,13 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4138033230913889</v>
+        <v>0.4024662703449913</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2832255831066867</v>
+        <v>0.2659359910638424</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3329161074322894</v>
+        <v>0.4042814630366958</v>
       </c>
       <c r="K15" s="4">
         <v>82.44259549973845</v>
@@ -5010,13 +5010,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3178043301325631</v>
+        <v>0.3162228713992378</v>
       </c>
       <c r="I16" s="4">
-        <v>0.197216408612479</v>
+        <v>0.1944993774898234</v>
       </c>
       <c r="J16" s="4">
-        <v>0.201508847468796</v>
+        <v>0.2058957588132702</v>
       </c>
       <c r="K16" s="4">
         <v>83.23443223443243</v>
@@ -5060,13 +5060,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3814395929124022</v>
+        <v>0.3807180183273653</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2319584808578825</v>
+        <v>0.2318801414238271</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2221489429279053</v>
+        <v>0.2222863400546437</v>
       </c>
       <c r="K17" s="4">
         <v>75.83453689167965</v>
@@ -5110,13 +5110,13 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H18" s="4">
-        <v>0.2576246017923318</v>
+        <v>0.2573906395496096</v>
       </c>
       <c r="I18" s="4">
-        <v>0.1644159293920417</v>
+        <v>0.1641409566152179</v>
       </c>
       <c r="J18" s="4">
-        <v>0.1691390060296277</v>
+        <v>0.1690748959043045</v>
       </c>
       <c r="K18" s="4">
         <v>85.74369440083737</v>
@@ -5160,13 +5160,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <v>0.3809474344195742</v>
+        <v>0.3809522217933448</v>
       </c>
       <c r="I19" s="4">
-        <v>0.1858671024960618</v>
+        <v>0.1858067423925404</v>
       </c>
       <c r="J19" s="4">
-        <v>0.1863604099511847</v>
+        <v>0.1861145270208745</v>
       </c>
       <c r="K19" s="4">
         <v>77.27001569858737</v>
@@ -5210,13 +5210,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <v>0.3132619815923943</v>
+        <v>0.3120709086774421</v>
       </c>
       <c r="I20" s="4">
-        <v>0.1899068012168525</v>
+        <v>0.1856405701032746</v>
       </c>
       <c r="J20" s="4">
-        <v>0.1834285612948555</v>
+        <v>0.1796481879371845</v>
       </c>
       <c r="K20" s="4">
         <v>82.66666666666679</v>
@@ -5260,13 +5260,13 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H21" s="4">
-        <v>0.7401082398251411</v>
+        <v>0.7340166796073528</v>
       </c>
       <c r="I21" s="4">
-        <v>0.2496140927409333</v>
+        <v>0.2462244253670296</v>
       </c>
       <c r="J21" s="4">
-        <v>0.4166953105892792</v>
+        <v>0.4163608507932913</v>
       </c>
       <c r="K21" s="4">
         <v>63.17844060701196</v>
@@ -5310,13 +5310,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <v>0.3131049934382497</v>
+        <v>0.3108368102080243</v>
       </c>
       <c r="I22" s="4">
-        <v>0.1451969747908615</v>
+        <v>0.1423064949542932</v>
       </c>
       <c r="J22" s="4">
-        <v>0.2806006258224383</v>
+        <v>0.2777817972277644</v>
       </c>
       <c r="K22" s="4">
         <v>86.97624280481449</v>
@@ -5360,13 +5360,13 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="H23" s="4">
-        <v>0.9876066861938452</v>
+        <v>0.9848126350957376</v>
       </c>
       <c r="I23" s="4">
-        <v>0.2695408825334226</v>
+        <v>0.2691425627657144</v>
       </c>
       <c r="J23" s="4">
-        <v>0.4762095147727832</v>
+        <v>0.4760741532562779</v>
       </c>
       <c r="K23" s="4">
         <v>51.79392987964418</v>
@@ -5410,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <v>0.2539374515673265</v>
+        <v>0.253596088076777</v>
       </c>
       <c r="I24" s="4">
-        <v>0.1529264205760139</v>
+        <v>0.1513075154112936</v>
       </c>
       <c r="J24" s="4">
-        <v>0.1874922639116891</v>
+        <v>0.1857224414994377</v>
       </c>
       <c r="K24" s="4">
         <v>85.11261119832555</v>
@@ -5442,13 +5442,13 @@
         <v>39</v>
       </c>
       <c r="B25" s="3">
-        <v>85.84615384615385</v>
+        <v>85.23076923076923</v>
       </c>
       <c r="C25" s="3">
         <v>2.153846153846154</v>
       </c>
       <c r="D25" s="3">
-        <v>12</v>
+        <v>12.61538461538461</v>
       </c>
       <c r="E25" s="3">
         <v>2.461538461538462</v>
@@ -5457,16 +5457,16 @@
         <v>9.230769230769232</v>
       </c>
       <c r="G25" s="3">
-        <v>0.3076923076923077</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="H25" s="4">
-        <v>0.3133186982878093</v>
+        <v>0.2881412477545617</v>
       </c>
       <c r="I25" s="4">
-        <v>0.2419718213886315</v>
+        <v>0.199772642674057</v>
       </c>
       <c r="J25" s="4">
-        <v>0.2571419152927938</v>
+        <v>0.2316738484265318</v>
       </c>
       <c r="K25" s="4">
         <v>85.04594453165886</v>
@@ -5653,16 +5653,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08987090723391628</v>
+        <v>-0.08592623266602573</v>
       </c>
       <c r="O3" s="5">
         <v>146</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2154349022235531</v>
+        <v>0.2153756836476111</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1430590108607807</v>
+        <v>0.1430199152901597</v>
       </c>
       <c r="R3" s="5">
         <v>146</v>
@@ -5712,16 +5712,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.103788506748059</v>
+        <v>-0.09476459190183562</v>
       </c>
       <c r="O4" s="5">
         <v>150</v>
       </c>
       <c r="P4" s="4">
-        <v>0.300074731605362</v>
+        <v>0.2996649470312501</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1853428428522035</v>
+        <v>0.1848367420746709</v>
       </c>
       <c r="R4" s="5">
         <v>149</v>
@@ -5894,16 +5894,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2386808447308738</v>
+        <v>-0.2295764584741278</v>
       </c>
       <c r="O3" s="5">
         <v>129</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3782744017457666</v>
+        <v>0.3784748949200185</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.174355489515992</v>
+        <v>0.1742849128783428</v>
       </c>
       <c r="R3" s="5">
         <v>129</v>
@@ -5953,16 +5953,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05233378975132903</v>
+        <v>-0.05479335078856451</v>
       </c>
       <c r="O4" s="5">
         <v>130</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3836369672950721</v>
+        <v>0.3834448408078646</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.197290164607054</v>
+        <v>0.1972399424489366</v>
       </c>
       <c r="R4" s="5">
         <v>130</v>
@@ -6135,16 +6135,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05731164827214132</v>
+        <v>-0.003663669053949548</v>
       </c>
       <c r="O3" s="5">
         <v>133</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3168204008139716</v>
+        <v>0.3158533241015183</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1731668260222488</v>
+        <v>0.1671893563809828</v>
       </c>
       <c r="R3" s="5">
         <v>133</v>
@@ -6194,16 +6194,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06004697269541207</v>
+        <v>-0.03087822230710913</v>
       </c>
       <c r="O4" s="5">
         <v>141</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3096815968200665</v>
+        <v>0.3082651450100073</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2056969905848122</v>
+        <v>0.2030449064512519</v>
       </c>
       <c r="R4" s="5">
         <v>141</v>
@@ -6376,16 +6376,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1628822943787176</v>
+        <v>0.218447054024729</v>
       </c>
       <c r="O3" s="5">
         <v>110</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4929198543541833</v>
+        <v>0.4951562681074623</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1543223708952885</v>
+        <v>0.1481842010041241</v>
       </c>
       <c r="R3" s="5">
         <v>110</v>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3143797344637121</v>
+        <v>0.2539635880793014</v>
       </c>
       <c r="O4" s="5">
         <v>99</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9888224795274009</v>
+        <v>0.9743515380918106</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3565741886901265</v>
+        <v>0.3562695751621275</v>
       </c>
       <c r="R4" s="5">
         <v>98</v>
@@ -6617,16 +6617,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4392626978035036</v>
+        <v>-0.4014169661664937</v>
       </c>
       <c r="O3" s="5">
         <v>141</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2665921198403519</v>
+        <v>0.2620301826733962</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1283850132848333</v>
+        <v>0.122574465614707</v>
       </c>
       <c r="R3" s="5">
         <v>141</v>
@@ -6676,16 +6676,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3113076583162423</v>
+        <v>-0.3096986062186176</v>
       </c>
       <c r="O4" s="5">
         <v>143</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3599049835398382</v>
+        <v>0.359944713221261</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1617738039681342</v>
+        <v>0.1617625518555633</v>
       </c>
       <c r="R4" s="5">
         <v>143</v>
@@ -6858,16 +6858,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4162763209220244</v>
+        <v>0.4297038002394926</v>
       </c>
       <c r="O3" s="5">
         <v>90</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6303684668056216</v>
+        <v>0.6326465463701815</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1718441852404744</v>
+        <v>0.170936073144715</v>
       </c>
       <c r="R3" s="5">
         <v>90</v>
@@ -6917,16 +6917,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4149701450443926</v>
+        <v>0.3949796204208269</v>
       </c>
       <c r="O4" s="5">
         <v>67</v>
       </c>
       <c r="P4" s="4">
-        <v>1.347050079775823</v>
+        <v>1.339152588566513</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4048132326313509</v>
+        <v>0.4051207791640211</v>
       </c>
       <c r="R4" s="5">
         <v>65</v>
@@ -7099,16 +7099,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2870719996060959</v>
+        <v>-0.2595715841239663</v>
       </c>
       <c r="O3" s="5">
         <v>136</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1731668059535966</v>
+        <v>0.1723176236841646</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1227870378018083</v>
+        <v>0.120766927881625</v>
       </c>
       <c r="R3" s="5">
         <v>136</v>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3078994064678701</v>
+        <v>-0.2791600697576655</v>
       </c>
       <c r="O4" s="5">
         <v>141</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3352066814132399</v>
+        <v>0.3353762713853933</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1819970309114178</v>
+        <v>0.1807651033831725</v>
       </c>
       <c r="R4" s="5">
         <v>141</v>
@@ -7340,22 +7340,22 @@
         <v>11</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.248864851469947</v>
+        <v>-1.125442554632883</v>
       </c>
       <c r="O3" s="5">
         <v>139</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2923312255999326</v>
+        <v>0.2559346645141989</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2388376193747755</v>
+        <v>0.184525245976968</v>
       </c>
       <c r="R3" s="5">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7399,22 +7399,22 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9099076630468238</v>
+        <v>-0.810364069502576</v>
       </c>
       <c r="O4" s="5">
         <v>141</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3344357232762284</v>
+        <v>0.3205466370643094</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2450393382532565</v>
+        <v>0.2146933094419227</v>
       </c>
       <c r="R4" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8629,13 +8629,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C3" s="5">
         <v>12</v>
       </c>
       <c r="D3" s="5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" s="5">
         <v>6</v>
@@ -8644,7 +8644,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
         <v>6</v>
@@ -9597,13 +9597,13 @@
         <v>39</v>
       </c>
       <c r="B25" s="5">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C25" s="5">
         <v>7</v>
       </c>
       <c r="D25" s="5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="5">
         <v>8</v>
@@ -9612,7 +9612,7 @@
         <v>30</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="5">
         <v>8</v>
@@ -9795,22 +9795,22 @@
         <v>19</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.402179691584727</v>
+        <v>-1.243038383846908</v>
       </c>
       <c r="O3" s="5">
         <v>137</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4166697305084675</v>
+        <v>0.3868213475609008</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.355131674855311</v>
+        <v>0.3066916206774418</v>
       </c>
       <c r="R3" s="5">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -9854,22 +9854,22 @@
         <v>7</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.063663131132687</v>
+        <v>-1.004836729628124</v>
       </c>
       <c r="O4" s="5">
         <v>141</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4084242588422744</v>
+        <v>0.4035485919470459</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2948420471966439</v>
+        <v>0.27566116678595</v>
       </c>
       <c r="R4" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10036,16 +10036,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01300060871079523</v>
+        <v>-0.012489063450289</v>
       </c>
       <c r="O3" s="5">
         <v>107</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4881837800191215</v>
+        <v>0.4882308547363459</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2203245020392124</v>
+        <v>0.2203197212423853</v>
       </c>
       <c r="R3" s="5">
         <v>107</v>
@@ -10095,16 +10095,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1157389194321866</v>
+        <v>0.1280198586065922</v>
       </c>
       <c r="O4" s="5">
         <v>114</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5443761622419219</v>
+        <v>0.5458421468832698</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2475746514777396</v>
+        <v>0.2475033420778295</v>
       </c>
       <c r="R4" s="5">
         <v>114</v>
@@ -10277,16 +10277,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04084964334964236</v>
+        <v>0.09450498792875806</v>
       </c>
       <c r="O3" s="5">
         <v>128</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3452880003498512</v>
+        <v>0.3458214490311394</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2933115155384715</v>
+        <v>0.2899964481097914</v>
       </c>
       <c r="R3" s="5">
         <v>128</v>
@@ -10336,16 +10336,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1479632107162064</v>
+        <v>0.1426119246197644</v>
       </c>
       <c r="O4" s="5">
         <v>132</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3398090142223275</v>
+        <v>0.3396060964658621</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2829651005660822</v>
+        <v>0.2828782253224336</v>
       </c>
       <c r="R4" s="5">
         <v>132</v>
@@ -10518,16 +10518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1313668290281663</v>
+        <v>-0.1044537219709412</v>
       </c>
       <c r="O3" s="5">
         <v>139</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2561117450490174</v>
+        <v>0.2558934615499224</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.175699041075233</v>
+        <v>0.1742813514874932</v>
       </c>
       <c r="R3" s="5">
         <v>139</v>
@@ -10577,16 +10577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.09750866148062573</v>
+        <v>-0.1134347854852535</v>
       </c>
       <c r="O4" s="5">
         <v>136</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4390251903147274</v>
+        <v>0.4377715731650894</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2037539578729506</v>
+        <v>0.2027290940330767</v>
       </c>
       <c r="R4" s="5">
         <v>136</v>
@@ -10759,16 +10759,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03965597258268876</v>
+        <v>-0.06011313223693548</v>
       </c>
       <c r="O3" s="5">
         <v>120</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3714041152470423</v>
+        <v>0.368249995637536</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1800407026538904</v>
+        <v>0.1789954071295668</v>
       </c>
       <c r="R3" s="5">
         <v>120</v>
@@ -10818,16 +10818,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01342714790855922</v>
+        <v>-0.04535649388063234</v>
       </c>
       <c r="O4" s="5">
         <v>125</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3772085302826998</v>
+        <v>0.3751905749800485</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2248720204741418</v>
+        <v>0.2227710239408605</v>
       </c>
       <c r="R4" s="5">
         <v>125</v>
